--- a/SQExcel.Portal/src/content/docs/ja/docs/images/io-operations/io-operations.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/io-operations/io-operations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\io-operations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\io-operations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AE1563-7DB1-4911-BC5E-9F182909F790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14C37D0-93BC-42B0-A21C-148A01553672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1780" windowWidth="18750" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1370" yWindow="110" windowWidth="20510" windowHeight="14610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IO-OPERATONS" sheetId="3" r:id="rId1"/>
@@ -2799,876 +2799,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>127312</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="5" name="グループ化 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87E0D2DC-51AE-4265-ACD6-DE2307542D7D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="694766"/>
-          <a:ext cx="10650071" cy="6611781"/>
-          <a:chOff x="469900" y="685801"/>
-          <a:chExt cx="10801350" cy="6528111"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="4" name="図 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C7EB33D-8527-7192-19E3-710732020C13}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="685801"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="正方形/長方形 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D554971F-9516-4C49-99EC-A8B25F6AB9AB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3503766" y="1188283"/>
-            <a:ext cx="5126270" cy="311771"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AF9929-E6F7-09B2-5AA1-ACE0141BF4A4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="514095" y="1210981"/>
-            <a:ext cx="2776058" cy="281507"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="四角形: 角を丸くする 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A107644-EDDF-4649-B573-0A55B7920A2C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2747141" y="997572"/>
-            <a:ext cx="471047" cy="266690"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>①</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="四角形: 角を丸くする 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{639C423F-B905-48E4-BFD5-9ED54855C495}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7662784" y="1012705"/>
-            <a:ext cx="478044" cy="266690"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="正方形/長方形 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40B15368-20FE-4093-BF27-69BF9F837E0C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="531774" y="1586309"/>
-            <a:ext cx="2846771" cy="3867050"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78369C21-6A54-4F6B-A59E-39A18C18526A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2451167" y="5232385"/>
-            <a:ext cx="471046" cy="260673"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>②</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="四角形: 角を丸くする 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7388A5E-885A-4865-87D7-31CC81038B81}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8531659" y="5566024"/>
-            <a:ext cx="478042" cy="266689"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>④</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="正方形/長方形 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19DAEFCD-6625-4858-A6BC-2BE1C130D842}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="631951" y="6688414"/>
-            <a:ext cx="2776058" cy="281507"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1DC0429-CCF0-4895-844E-E6F815838269}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2834844" y="6871560"/>
-            <a:ext cx="471047" cy="266690"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>⑤</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="正方形/長方形 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6EDA4DC-7CB2-4153-81F4-89B1E80B0DE6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4076241" y="6695982"/>
-            <a:ext cx="3613708" cy="319337"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="正方形/長方形 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A14B7BC-C1E7-43FE-8863-FD9BAB31CE72}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3503766" y="1568151"/>
-            <a:ext cx="7704136" cy="5005216"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:prstDash val="sysDash"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="正方形/長方形 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C382D053-3D37-4029-AA9F-F3FA9775CB4C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7814482" y="6695982"/>
-            <a:ext cx="3260834" cy="319337"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="四角形: 角を丸くする 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7DDA07B-969B-432A-8928-ED832849DE94}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5897483" y="6939657"/>
-            <a:ext cx="471047" cy="266690"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>⑥</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="四角形: 角を丸くする 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9425E13F-18DB-5F56-FE13-A2392A3512E3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9783043" y="6947222"/>
-            <a:ext cx="471047" cy="266690"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>⑦</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>231587</xdr:colOff>
       <xdr:row>39</xdr:row>
@@ -3713,7 +2843,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3834,7 +2964,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3863,7 +2993,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4082,7 +3212,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4111,7 +3241,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4798,7 +3928,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4834,7 +3964,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -5054,7 +4184,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -5293,7 +4423,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -5322,7 +4452,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -5407,7 +4537,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -5526,450 +4656,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>18143</xdr:colOff>
-      <xdr:row>264</xdr:row>
-      <xdr:rowOff>9072</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>10886</xdr:colOff>
-      <xdr:row>293</xdr:row>
-      <xdr:rowOff>146203</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="29" name="グループ化 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CDAD39E-DCD0-6A1B-ADB5-A0F45128E96D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="481319" y="61148366"/>
-          <a:ext cx="10645802" cy="6853190"/>
-          <a:chOff x="488043" y="60384872"/>
-          <a:chExt cx="10800443" cy="6766531"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="101" name="図 100">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF2F02C-B502-4563-E506-2D2BBA1D21BA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="488043" y="60384872"/>
-            <a:ext cx="10800443" cy="6766531"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="102" name="矢印: 下カーブ 101">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{348FD0A8-B75F-FB1A-7D5C-FF2278F06BAB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3010359" y="62613619"/>
-            <a:ext cx="2664374" cy="523894"/>
-          </a:xfrm>
-          <a:prstGeom prst="curvedDownArrow">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent2"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="103" name="正方形/長方形 102">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF9F19B3-73C1-4C18-9E6F-9E8C5EC1F101}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="542678" y="62514610"/>
-            <a:ext cx="2702612" cy="2524005"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="104" name="吹き出し: 四角形 103">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97B0BA6E-21E4-48AD-9DCB-B0FD95C90062}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5042785" y="63200523"/>
-            <a:ext cx="1753785" cy="439271"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -21368"/>
-              <a:gd name="adj2" fmla="val -47993"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>ドラッグ＆ドロップ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2</xdr:colOff>
-      <xdr:row>302</xdr:row>
-      <xdr:rowOff>9074</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228602</xdr:colOff>
-      <xdr:row>331</xdr:row>
-      <xdr:rowOff>146204</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="114" name="グループ化 113">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D407800C-84B8-9541-4B5C-D38150BC2B0D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463178" y="69948721"/>
-          <a:ext cx="10650071" cy="6853189"/>
-          <a:chOff x="488044" y="68394945"/>
-          <a:chExt cx="10800443" cy="6766530"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="113" name="図 112">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD8D2835-D014-2CD8-2A17-C8E14C070087}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="488044" y="68394945"/>
-            <a:ext cx="10800443" cy="6766530"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="107" name="正方形/長方形 106">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58D4C6AD-D50B-4940-8373-937BA9BE8E90}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="768349" y="70680943"/>
-            <a:ext cx="2593522" cy="2340428"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="108" name="コネクタ: カギ線 107">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{983606E0-3FB6-4A12-953F-1BAADA50E4BD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="109" idx="2"/>
-            <a:endCxn id="107" idx="3"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="5400000">
-            <a:off x="4262212" y="69991060"/>
-            <a:ext cx="959756" cy="2760436"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="109" name="正方形/長方形 108">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A36DBD78-60DE-40C0-8D24-D78BCB131BA6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3551464" y="69519801"/>
-            <a:ext cx="5141686" cy="1371600"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>352</xdr:row>
@@ -5995,7 +4681,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6058,7 +4744,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6087,7 +4773,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6102,232 +4788,6 @@
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>410</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>439</xdr:row>
-      <xdr:rowOff>137132</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="50" name="グループ化 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19205CF2-352A-5304-4CE0-83AE990F063F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="94951177"/>
-          <a:ext cx="10650071" cy="6853190"/>
-          <a:chOff x="469900" y="93764101"/>
-          <a:chExt cx="10801350" cy="6766531"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="49" name="図 48">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13399EA5-370C-0D49-5A87-9E1C5B025C72}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="93764101"/>
-            <a:ext cx="10801350" cy="6766531"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="26" name="矢印: 下カーブ 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17018B2B-294C-42D5-9605-838548C00095}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6966397" y="95294174"/>
-            <a:ext cx="2666595" cy="521331"/>
-          </a:xfrm>
-          <a:prstGeom prst="curvedDownArrow">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent2"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="27" name="正方形/長方形 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A43230A-073E-4EDE-AEAC-3B7C4DBADA77}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3477583" y="95834814"/>
-            <a:ext cx="5251854" cy="826700"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="吹き出し: 四角形 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05E670B2-1166-4FD3-BAEB-08FE1E8173B4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8982039" y="95825372"/>
-            <a:ext cx="1753956" cy="437401"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -21368"/>
-              <a:gd name="adj2" fmla="val -47993"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>ドラッグ＆ドロップ</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -6377,7 +4837,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6595,7 +5055,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6875,7 +5335,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6904,7 +5364,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -6919,253 +5379,6 @@
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>216648</xdr:colOff>
-      <xdr:row>507</xdr:row>
-      <xdr:rowOff>134472</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>213660</xdr:colOff>
-      <xdr:row>536</xdr:row>
-      <xdr:rowOff>11570</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="98" name="グループ化 97">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCB51C71-C478-D09D-A734-EB0AA16A9359}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="448236" y="117549707"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="469900" y="115280143"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="84" name="図 83">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02A4869F-2DAB-25E6-377D-BD17A2300DC3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="115280143"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="78" name="図 77">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB700047-7159-C307-5C5B-E7EBBCE8415A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3498476" y="117374896"/>
-            <a:ext cx="5004548" cy="2078503"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="85" name="正方形/長方形 84">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AA6F553-9B82-4CFB-8D65-9BBBBE8E0223}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4688168" y="115797106"/>
-            <a:ext cx="350370" cy="295835"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="87" name="コネクタ: カギ線 86">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA37B4C3-89B5-4DC2-8716-E8B6D5CAE634}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="85" idx="2"/>
-            <a:endCxn id="93" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="16200000" flipH="1">
-            <a:off x="4780541" y="116175753"/>
-            <a:ext cx="1244600" cy="1078975"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="93" name="正方形/長方形 92">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB4476E9-D18D-484F-953D-7CF355F3D76D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5896161" y="117337541"/>
-            <a:ext cx="92334" cy="94388"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="0000FF"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -7215,7 +5428,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7334,7 +5547,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7363,7 +5576,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7484,855 +5697,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>586</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>614</xdr:row>
-      <xdr:rowOff>108688</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="130" name="グループ化 129">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE12C011-F0BF-9216-4E83-9AB78798A378}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="135710707"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="469900" y="134696201"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="121" name="図 120">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB423A9B-DD57-C6BD-A84E-CFE5F8B77347}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="134696201"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="123" name="正方形/長方形 122">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A336CE09-0E76-4FA1-BE98-53690533E185}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5251075" y="135243048"/>
-            <a:ext cx="3296772" cy="228600"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="125" name="正方形/長方形 124">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{043A8E0C-6BF1-437D-86BF-CFA0EF59915D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3476064" y="135561294"/>
-            <a:ext cx="7648763" cy="1709271"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="126" name="コネクタ: カギ線 125">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA598099-206F-41B6-9986-717069EE88EB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="123" idx="3"/>
-            <a:endCxn id="127" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8547847" y="135358842"/>
-            <a:ext cx="621961" cy="150158"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="127" name="正方形/長方形 126">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{117807E1-9873-4959-980E-1BBA32EE7F0D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9120279" y="135509000"/>
-            <a:ext cx="95696" cy="94388"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="0000FF"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>216647</xdr:colOff>
-      <xdr:row>620</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>213659</xdr:colOff>
-      <xdr:row>648</xdr:row>
-      <xdr:rowOff>108688</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="132" name="グループ化 131">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB31E91-5330-FD6D-642E-B6AF4EB2604D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="448235" y="143584706"/>
-          <a:ext cx="10650071" cy="6593158"/>
-          <a:chOff x="451597" y="142468600"/>
-          <a:chExt cx="10804712" cy="6509488"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="122" name="図 121">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2D19CD-CD79-6D37-2ED5-2386030393C2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="451597" y="142468600"/>
-            <a:ext cx="10804712" cy="6509488"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="131" name="正方形/長方形 130">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE49CCD3-4461-4591-A8A0-956876D342F3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5206251" y="142963152"/>
-            <a:ext cx="3356538" cy="767977"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>655</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>683</xdr:row>
-      <xdr:rowOff>108688</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="141" name="グループ化 140">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8EE9751-1189-5C4C-F3F5-DAF23A0D8739}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="151690295"/>
-          <a:ext cx="10650071" cy="6593158"/>
-          <a:chOff x="469900" y="149783801"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="134" name="図 133">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566E93CD-0684-6C45-A055-BBB50BB1F797}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="149783801"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="133" name="図 132">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488002EC-4032-5376-6B2E-96A9B793D843}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4208496" y="152241622"/>
-            <a:ext cx="3648603" cy="1622613"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="135" name="正方形/長方形 134">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{375F0BF7-F686-4C9C-88CB-29097B23A2D4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4948890" y="150293295"/>
-            <a:ext cx="302187" cy="288364"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="136" name="コネクタ: カギ線 135">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AB63A95-6413-46B9-A326-0226AD795482}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="135" idx="2"/>
-            <a:endCxn id="133" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="16200000" flipH="1">
-            <a:off x="4735569" y="150944393"/>
-            <a:ext cx="1659963" cy="934495"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>224117</xdr:colOff>
-      <xdr:row>824</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>221129</xdr:colOff>
-      <xdr:row>852</xdr:row>
-      <xdr:rowOff>108688</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="156" name="グループ化 155">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A8F4E53-8F94-77E6-2CF6-C8044CF00ED0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="455705" y="190828707"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="469900" y="158254701"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="144" name="グループ化 143">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28BC9862-AA6D-6BBF-C576-C3DA9CC350E6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="469900" y="158254701"/>
-            <a:ext cx="10801350" cy="6509487"/>
-            <a:chOff x="469900" y="158242001"/>
-            <a:chExt cx="10801350" cy="6509487"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="142" name="図 141">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A52EEBA-FD57-4319-03FF-BBA4E09C1C99}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="469900" y="158242001"/>
-              <a:ext cx="10801350" cy="6509487"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="143" name="図 142">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC367FB-C520-C995-14C7-60DB4BAEF146}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2424206" y="158472548"/>
-              <a:ext cx="1804985" cy="660807"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="145" name="正方形/長方形 144">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F74589-E594-4676-BCF5-91CC8FBD431F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2448890" y="158704170"/>
-            <a:ext cx="1705390" cy="206512"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="146" name="コネクタ: カギ線 145">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B6395C5-5D71-4675-BC97-1592D6659DE8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="153" idx="1"/>
-            <a:endCxn id="145" idx="2"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="10800000">
-            <a:off x="3300344" y="158910683"/>
-            <a:ext cx="1890645" cy="2300064"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="153" name="正方形/長方形 152">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD13DF62-9033-4F12-A60D-EFEE7C2EFB6D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5190988" y="161163552"/>
-            <a:ext cx="92334" cy="96597"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="0000FF"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>216647</xdr:colOff>
       <xdr:row>713</xdr:row>
@@ -8357,7 +5721,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="448235" y="165301706"/>
+          <a:off x="448235" y="165122412"/>
           <a:ext cx="10650071" cy="6414614"/>
           <a:chOff x="477371" y="166969141"/>
           <a:chExt cx="10804712" cy="6333932"/>
@@ -8377,7 +5741,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -8509,21 +5873,21 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>746</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>774</xdr:row>
-      <xdr:rowOff>108689</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>127312</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="117" name="グループ化 116">
+        <xdr:cNvPr id="140" name="グループ化 139">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60B1A0CE-EA93-D0C9-DA05-2A61F0DFEB35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BBF9F90-4924-FDAC-6B86-35A2D9ECDCB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8531,18 +5895,873 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="172764825"/>
-          <a:ext cx="10650071" cy="6593158"/>
-          <a:chOff x="469900" y="174040801"/>
-          <a:chExt cx="10801350" cy="6509487"/>
+          <a:off x="463176" y="694766"/>
+          <a:ext cx="10650071" cy="6611781"/>
+          <a:chOff x="469900" y="685801"/>
+          <a:chExt cx="10801350" cy="6528111"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="5" name="グループ化 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87E0D2DC-51AE-4265-ACD6-DE2307542D7D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="685801"/>
+            <a:ext cx="10801350" cy="6528111"/>
+            <a:chOff x="469900" y="685801"/>
+            <a:chExt cx="10801350" cy="6528111"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="図 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C7EB33D-8527-7192-19E3-710732020C13}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="685801"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="正方形/長方形 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D554971F-9516-4C49-99EC-A8B25F6AB9AB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3503766" y="1188283"/>
+              <a:ext cx="5126270" cy="311771"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="正方形/長方形 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AF9929-E6F7-09B2-5AA1-ACE0141BF4A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="514095" y="1210981"/>
+              <a:ext cx="2776058" cy="281507"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="四角形: 角を丸くする 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A107644-EDDF-4649-B573-0A55B7920A2C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2747141" y="997572"/>
+              <a:ext cx="471047" cy="266690"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9" name="四角形: 角を丸くする 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{639C423F-B905-48E4-BFD5-9ED54855C495}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7662784" y="1012705"/>
+              <a:ext cx="478044" cy="266690"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40B15368-20FE-4093-BF27-69BF9F837E0C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="531774" y="1586309"/>
+              <a:ext cx="2846771" cy="3867050"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78369C21-6A54-4F6B-A59E-39A18C18526A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2451167" y="5232385"/>
+              <a:ext cx="471046" cy="260673"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="四角形: 角を丸くする 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7388A5E-885A-4865-87D7-31CC81038B81}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8531659" y="5566024"/>
+              <a:ext cx="478042" cy="266689"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19DAEFCD-6625-4858-A6BC-2BE1C130D842}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="631951" y="6688414"/>
+              <a:ext cx="2776058" cy="281507"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1DC0429-CCF0-4895-844E-E6F815838269}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2834844" y="6871560"/>
+              <a:ext cx="471047" cy="266690"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑤</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="正方形/長方形 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6EDA4DC-7CB2-4153-81F4-89B1E80B0DE6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4076241" y="6695982"/>
+              <a:ext cx="3613708" cy="319337"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="正方形/長方形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A14B7BC-C1E7-43FE-8863-FD9BAB31CE72}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3503766" y="1568151"/>
+              <a:ext cx="7704136" cy="5005216"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="正方形/長方形 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C382D053-3D37-4029-AA9F-F3FA9775CB4C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7814482" y="6695982"/>
+              <a:ext cx="3260834" cy="319337"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="四角形: 角を丸くする 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7DDA07B-969B-432A-8928-ED832849DE94}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5897483" y="6939657"/>
+              <a:ext cx="471047" cy="266690"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑥</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="四角形: 角を丸くする 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9425E13F-18DB-5F56-FE13-A2392A3512E3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9783043" y="6947222"/>
+              <a:ext cx="471047" cy="266690"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑦</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="80" name="図 79">
+          <xdr:cNvPr id="57" name="図 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05FD41FF-CD7D-70ED-9970-DE10C6CA2C18}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE9D447-CD77-4C6A-B0E3-79C083213AB5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8551,241 +6770,2366 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="174040801"/>
-            <a:ext cx="10801350" cy="6509487"/>
+            <a:off x="499782" y="715683"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="86" name="正方形/長方形 85">
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>9072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>293</xdr:row>
+      <xdr:rowOff>146203</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="148" name="グループ化 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEFB75B7-4660-5D3D-83DE-AA37E66CC55E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="481319" y="61148366"/>
+          <a:ext cx="10645802" cy="6853190"/>
+          <a:chOff x="488043" y="60384872"/>
+          <a:chExt cx="10800443" cy="6766531"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="29" name="グループ化 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{516E4237-5026-497D-98CB-CD1C1EB60101}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CDAD39E-DCD0-6A1B-ADB5-A0F45128E96D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="488043" y="60384872"/>
+            <a:ext cx="10800443" cy="6766531"/>
+            <a:chOff x="488043" y="60384872"/>
+            <a:chExt cx="10800443" cy="6766531"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="101" name="図 100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF2F02C-B502-4563-E506-2D2BBA1D21BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="488043" y="60384872"/>
+              <a:ext cx="10800443" cy="6766531"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="102" name="矢印: 下カーブ 101">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{348FD0A8-B75F-FB1A-7D5C-FF2278F06BAB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3010359" y="62613619"/>
+              <a:ext cx="2664374" cy="523894"/>
+            </a:xfrm>
+            <a:prstGeom prst="curvedDownArrow">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent2"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="103" name="正方形/長方形 102">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF9F19B3-73C1-4C18-9E6F-9E8C5EC1F101}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="542678" y="62514610"/>
+              <a:ext cx="2702612" cy="2524005"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="104" name="吹き出し: 四角形 103">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97B0BA6E-21E4-48AD-9DCB-B0FD95C90062}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5042785" y="63200523"/>
+              <a:ext cx="1753785" cy="439271"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -21368"/>
+                <a:gd name="adj2" fmla="val -47993"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>ドラッグ＆ドロップ</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="147" name="図 146">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D961D4C-7A7B-4AB8-9462-CCD727B601E9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="727261" y="177941942"/>
-            <a:ext cx="1219574" cy="194235"/>
+            <a:off x="507254" y="60413152"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="90" name="正方形/長方形 89">
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>9074</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228602</xdr:colOff>
+      <xdr:row>331</xdr:row>
+      <xdr:rowOff>146204</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="150" name="グループ化 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AC39F81-2A12-1347-B038-9C527ACE618A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463178" y="69948721"/>
+          <a:ext cx="10650071" cy="6853189"/>
+          <a:chOff x="469902" y="69071674"/>
+          <a:chExt cx="10801350" cy="6766530"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="114" name="グループ化 113">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4064515F-C050-4036-B58F-CC2F8BB98C18}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D407800C-84B8-9541-4B5C-D38150BC2B0D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469902" y="69071674"/>
+            <a:ext cx="10801350" cy="6766530"/>
+            <a:chOff x="488044" y="68394945"/>
+            <a:chExt cx="10800443" cy="6766530"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="113" name="図 112">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD8D2835-D014-2CD8-2A17-C8E14C070087}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="488044" y="68394945"/>
+              <a:ext cx="10800443" cy="6766530"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="107" name="正方形/長方形 106">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58D4C6AD-D50B-4940-8373-937BA9BE8E90}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="768349" y="70680943"/>
+              <a:ext cx="2593522" cy="2340428"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="108" name="コネクタ: カギ線 107">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{983606E0-3FB6-4A12-953F-1BAADA50E4BD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="109" idx="2"/>
+              <a:endCxn id="107" idx="3"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="5400000">
+              <a:off x="4262212" y="69991060"/>
+              <a:ext cx="959756" cy="2760436"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector2">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="109" name="正方形/長方形 108">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A36DBD78-60DE-40C0-8D24-D78BCB131BA6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3551464" y="69519801"/>
+              <a:ext cx="5141686" cy="1371600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="149" name="図 148">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBF84C24-6267-4A55-9592-557B31F9C25C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="686548" y="180103929"/>
-            <a:ext cx="2714811" cy="228601"/>
+            <a:off x="484841" y="69099953"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="97" name="正方形/長方形 96">
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>410</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>439</xdr:row>
+      <xdr:rowOff>137132</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="152" name="グループ化 151">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196AA263-A773-C0C6-E8FD-87CAB3C81A01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="94951177"/>
+          <a:ext cx="10650071" cy="6853190"/>
+          <a:chOff x="469900" y="93764101"/>
+          <a:chExt cx="10801350" cy="6766531"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="50" name="グループ化 49">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2F51C8-3752-4A73-BFFF-961B73705C78}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19205CF2-352A-5304-4CE0-83AE990F063F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="93764101"/>
+            <a:ext cx="10801350" cy="6766531"/>
+            <a:chOff x="469900" y="93764101"/>
+            <a:chExt cx="10801350" cy="6766531"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="49" name="図 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13399EA5-370C-0D49-5A87-9E1C5B025C72}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="93764101"/>
+              <a:ext cx="10801350" cy="6766531"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="矢印: 下カーブ 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17018B2B-294C-42D5-9605-838548C00095}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6966397" y="95294174"/>
+              <a:ext cx="2666595" cy="521331"/>
+            </a:xfrm>
+            <a:prstGeom prst="curvedDownArrow">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent2"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="正方形/長方形 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A43230A-073E-4EDE-AEAC-3B7C4DBADA77}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3477583" y="95834814"/>
+              <a:ext cx="5251854" cy="826700"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="吹き出し: 四角形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05E670B2-1166-4FD3-BAEB-08FE1E8173B4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8982039" y="95825372"/>
+              <a:ext cx="1753956" cy="437401"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -21368"/>
+                <a:gd name="adj2" fmla="val -47993"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>ドラッグ＆ドロップ</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="151" name="図 150">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A9A434B-B38B-47DC-BC53-597A1FA1263B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3598954" y="176652517"/>
-            <a:ext cx="5083363" cy="243542"/>
+            <a:off x="484841" y="93786512"/>
+            <a:ext cx="252070" cy="225938"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="116" name="正方形/長方形 115">
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216648</xdr:colOff>
+      <xdr:row>507</xdr:row>
+      <xdr:rowOff>134472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>213660</xdr:colOff>
+      <xdr:row>536</xdr:row>
+      <xdr:rowOff>11570</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="155" name="グループ化 154">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{874082CF-1BAB-61C9-86FF-4EA3571C556D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="448236" y="117549707"/>
+          <a:ext cx="10650071" cy="6593157"/>
+          <a:chOff x="451598" y="116085472"/>
+          <a:chExt cx="10804712" cy="6506498"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="98" name="グループ化 97">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D93FC66-492E-444A-ACA2-F24BB67745AA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCB51C71-C478-D09D-A734-EB0AA16A9359}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="451598" y="116085472"/>
+            <a:ext cx="10804712" cy="6506498"/>
+            <a:chOff x="469900" y="115280143"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="84" name="図 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02A4869F-2DAB-25E6-377D-BD17A2300DC3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="115280143"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="78" name="図 77">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB700047-7159-C307-5C5B-E7EBBCE8415A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3498476" y="117374896"/>
+              <a:ext cx="5004548" cy="2078503"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="85" name="正方形/長方形 84">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AA6F553-9B82-4CFB-8D65-9BBBBE8E0223}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4688168" y="115797106"/>
+              <a:ext cx="350370" cy="295835"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="87" name="コネクタ: カギ線 86">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA37B4C3-89B5-4DC2-8716-E8B6D5CAE634}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="85" idx="2"/>
+              <a:endCxn id="93" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="16200000" flipH="1">
+              <a:off x="4780541" y="116175753"/>
+              <a:ext cx="1244600" cy="1078975"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 50000"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="93" name="正方形/長方形 92">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB4476E9-D18D-484F-953D-7CF355F3D76D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5896161" y="117337541"/>
+              <a:ext cx="92334" cy="94388"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="154" name="図 153">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AFFA6E1-19BE-4F3C-97EF-3C2B531FE6B7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8767857" y="176180661"/>
-            <a:ext cx="1219574" cy="191247"/>
+            <a:off x="477371" y="116100413"/>
+            <a:ext cx="252070" cy="225938"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>586</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>614</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="158" name="グループ化 157">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC2793D9-D638-A67C-5D2B-1FD7DA3EA3CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="135710707"/>
+          <a:ext cx="10650071" cy="6593157"/>
+          <a:chOff x="469900" y="134010401"/>
+          <a:chExt cx="10801350" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="130" name="グループ化 129">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE12C011-F0BF-9216-4E83-9AB78798A378}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="134010401"/>
+            <a:ext cx="10801350" cy="6509487"/>
+            <a:chOff x="469900" y="134696201"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="121" name="図 120">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB423A9B-DD57-C6BD-A84E-CFE5F8B77347}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="134696201"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="123" name="正方形/長方形 122">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A336CE09-0E76-4FA1-BE98-53690533E185}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5251075" y="135243048"/>
+              <a:ext cx="3296772" cy="228600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="125" name="正方形/長方形 124">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{043A8E0C-6BF1-437D-86BF-CFA0EF59915D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3476064" y="135561294"/>
+              <a:ext cx="7648763" cy="1709271"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="126" name="コネクタ: カギ線 125">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA598099-206F-41B6-9986-717069EE88EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="123" idx="3"/>
+              <a:endCxn id="127" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8547847" y="135358842"/>
+              <a:ext cx="621961" cy="150158"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector2">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="127" name="正方形/長方形 126">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{117807E1-9873-4959-980E-1BBA32EE7F0D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9120279" y="135509000"/>
+              <a:ext cx="95696" cy="94388"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
             <a:solidFill>
-              <a:srgbClr val="FF0000"/>
+              <a:srgbClr val="FFC000"/>
             </a:solidFill>
-          </a:ln>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="157" name="図 156">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6396C40F-B586-4790-8883-44D73810B6B1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="492313" y="134032811"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216647</xdr:colOff>
+      <xdr:row>620</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>213659</xdr:colOff>
+      <xdr:row>648</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="160" name="グループ化 159">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6143382-0B30-0833-4724-D780BB4193CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="448235" y="143584706"/>
+          <a:ext cx="10650071" cy="6593158"/>
+          <a:chOff x="451597" y="141782800"/>
+          <a:chExt cx="10804712" cy="6509488"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="132" name="グループ化 131">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB31E91-5330-FD6D-642E-B6AF4EB2604D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="451597" y="141782800"/>
+            <a:ext cx="10804712" cy="6509488"/>
+            <a:chOff x="451597" y="142468600"/>
+            <a:chExt cx="10804712" cy="6509488"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="122" name="図 121">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2D19CD-CD79-6D37-2ED5-2386030393C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="451597" y="142468600"/>
+              <a:ext cx="10804712" cy="6509488"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
               <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="131" name="正方形/長方形 130">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE49CCD3-4461-4591-A8A0-956876D342F3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5206251" y="142963152"/>
+              <a:ext cx="3356538" cy="767977"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="159" name="図 158">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC90BB57-A912-4909-8023-A51CC126C4F5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="469900" y="141797741"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>655</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>683</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="162" name="グループ化 161">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF212615-6396-D5A9-2F56-ADAF81412300}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="151690295"/>
+          <a:ext cx="10650071" cy="6593158"/>
+          <a:chOff x="469900" y="149783801"/>
+          <a:chExt cx="10801350" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="141" name="グループ化 140">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8EE9751-1189-5C4C-F3F5-DAF23A0D8739}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="149783801"/>
+            <a:ext cx="10801350" cy="6509487"/>
+            <a:chOff x="469900" y="149783801"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="134" name="図 133">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{566E93CD-0684-6C45-A055-BBB50BB1F797}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="149783801"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="133" name="図 132">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488002EC-4032-5376-6B2E-96A9B793D843}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4208496" y="152241622"/>
+              <a:ext cx="3648603" cy="1622613"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="135" name="正方形/長方形 134">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{375F0BF7-F686-4C9C-88CB-29097B23A2D4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4948890" y="150293295"/>
+              <a:ext cx="302187" cy="288364"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="136" name="コネクタ: カギ線 135">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AB63A95-6413-46B9-A326-0226AD795482}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="135" idx="2"/>
+              <a:endCxn id="133" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="16200000" flipH="1">
+              <a:off x="4735569" y="150944393"/>
+              <a:ext cx="1659963" cy="934495"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 50000"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="161" name="図 160">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EF64632-CC56-4463-89AF-66D969BB19ED}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="492312" y="149806212"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>703</xdr:row>
+      <xdr:rowOff>176021</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="164" name="グループ化 163">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4D25572-A586-9324-7B49-1CA58B3CC7C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="159795883"/>
+          <a:ext cx="10650071" cy="3007373"/>
+          <a:chOff x="469900" y="157784801"/>
+          <a:chExt cx="10801350" cy="2970020"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="139" name="グループ化 138">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D118EF50-8AC2-7460-BCC8-0AAB43843234}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="157784801"/>
+            <a:ext cx="10801350" cy="2970020"/>
+            <a:chOff x="469900" y="157099001"/>
+            <a:chExt cx="10801350" cy="2971515"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="137" name="図 136">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F48E4675-205D-936B-1AC4-884485AC4E04}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="157099001"/>
+              <a:ext cx="10801350" cy="2971515"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="138" name="正方形/長方形 137">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16683198-05AC-4125-910E-AEF6CFBDB750}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5258546" y="157578612"/>
+              <a:ext cx="3356537" cy="663014"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="163" name="図 162">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8431067-0115-4A7D-9311-6C7AC0E10A7E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="484842" y="157807213"/>
+            <a:ext cx="252070" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>746</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>774</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="166" name="グループ化 165">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71980109-53A0-3C34-BBD2-F7754B042777}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="463176" y="172585530"/>
+          <a:ext cx="10650071" cy="6593158"/>
+          <a:chOff x="469900" y="170421301"/>
+          <a:chExt cx="10801350" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="117" name="グループ化 116">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60B1A0CE-EA93-D0C9-DA05-2A61F0DFEB35}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="170421301"/>
+            <a:ext cx="10801350" cy="6509487"/>
+            <a:chOff x="469900" y="174040801"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="80" name="図 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05FD41FF-CD7D-70ED-9970-DE10C6CA2C18}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="174040801"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="86" name="正方形/長方形 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{516E4237-5026-497D-98CB-CD1C1EB60101}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="727261" y="177941942"/>
+              <a:ext cx="1219574" cy="194235"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="90" name="正方形/長方形 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4064515F-C050-4036-B58F-CC2F8BB98C18}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="686548" y="180103929"/>
+              <a:ext cx="2714811" cy="228601"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="97" name="正方形/長方形 96">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2F51C8-3752-4A73-BFFF-961B73705C78}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3598954" y="176652517"/>
+              <a:ext cx="5083363" cy="243542"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="116" name="正方形/長方形 115">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D93FC66-492E-444A-ACA2-F24BB67745AA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8767857" y="176180661"/>
+              <a:ext cx="1219574" cy="191247"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="165" name="図 164">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11997C4-C0C5-4368-994B-750B363099F5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="492312" y="170443712"/>
+            <a:ext cx="252070" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -8804,10 +9148,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="129" name="グループ化 128">
+        <xdr:cNvPr id="168" name="グループ化 167">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C23A079-8EBF-343B-B6E4-C4577B013C06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1FAE2C7-BE0B-3CE5-EC87-90109AE1468E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8815,18 +9159,232 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="181580120"/>
+          <a:off x="463176" y="181400826"/>
           <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="469900" y="182270401"/>
-          <a:chExt cx="10801350" cy="6509487"/>
+          <a:chOff x="469900" y="179123044"/>
+          <a:chExt cx="10801350" cy="6509486"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="129" name="グループ化 128">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C23A079-8EBF-343B-B6E4-C4577B013C06}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469900" y="179123044"/>
+            <a:ext cx="10801350" cy="6509486"/>
+            <a:chOff x="469900" y="182270401"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="119" name="図 118">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A47B661-AB32-D77B-5888-3F0906B096A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="182270401"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="120" name="正方形/長方形 119">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615DF566-70FB-48F9-930E-D57F25305EF7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="664136" y="188311117"/>
+              <a:ext cx="2717130" cy="228551"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="124" name="正方形/長方形 123">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E6F03F-5DD4-4CD9-B676-1D6254883657}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3561603" y="184844765"/>
+              <a:ext cx="5082766" cy="243683"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="128" name="正方形/長方形 127">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1116A404-8E86-4DD5-BC1A-F30C1E277CEF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8767856" y="184417447"/>
+              <a:ext cx="1219302" cy="190717"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="119" name="図 118">
+          <xdr:cNvPr id="167" name="図 166">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A47B661-AB32-D77B-5888-3F0906B096A4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92793D2C-31BB-4227-9967-EA9E23FC5469}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -8835,208 +9393,43 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="182270401"/>
-            <a:ext cx="10801350" cy="6509487"/>
+            <a:off x="492312" y="179152923"/>
+            <a:ext cx="252070" cy="225938"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="120" name="正方形/長方形 119">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615DF566-70FB-48F9-930E-D57F25305EF7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="664136" y="188311117"/>
-            <a:ext cx="2717130" cy="228551"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="124" name="正方形/長方形 123">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E6F03F-5DD4-4CD9-B676-1D6254883657}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3561603" y="184844765"/>
-            <a:ext cx="5082766" cy="243683"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="128" name="正方形/長方形 127">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1116A404-8E86-4DD5-BC1A-F30C1E277CEF}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8767856" y="184417447"/>
-            <a:ext cx="1219302" cy="190717"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>690</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>224117</xdr:colOff>
+      <xdr:row>824</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>702</xdr:row>
-      <xdr:rowOff>228315</xdr:rowOff>
+      <xdr:colOff>221129</xdr:colOff>
+      <xdr:row>852</xdr:row>
+      <xdr:rowOff>108688</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="139" name="グループ化 138">
+        <xdr:cNvPr id="170" name="グループ化 169">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D118EF50-8AC2-7460-BCC8-0AAB43843234}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F19E4480-CF0B-AF05-7F1F-14304013F896}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9044,18 +9437,268 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="159795883"/>
-          <a:ext cx="10650071" cy="3007373"/>
-          <a:chOff x="469900" y="157099001"/>
-          <a:chExt cx="10801350" cy="2971515"/>
+          <a:off x="455705" y="190649413"/>
+          <a:ext cx="10650071" cy="6593157"/>
+          <a:chOff x="459067" y="188264801"/>
+          <a:chExt cx="10804712" cy="6509487"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="156" name="グループ化 155">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A8F4E53-8F94-77E6-2CF6-C8044CF00ED0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="459067" y="188264801"/>
+            <a:ext cx="10804712" cy="6509487"/>
+            <a:chOff x="469900" y="158254701"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="144" name="グループ化 143">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28BC9862-AA6D-6BBF-C576-C3DA9CC350E6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="469900" y="158254701"/>
+              <a:ext cx="10801350" cy="6509487"/>
+              <a:chOff x="469900" y="158242001"/>
+              <a:chExt cx="10801350" cy="6509487"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="142" name="図 141">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A52EEBA-FD57-4319-03FF-BBA4E09C1C99}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="469900" y="158242001"/>
+                <a:ext cx="10801350" cy="6509487"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="143" name="図 142">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC367FB-C520-C995-14C7-60DB4BAEF146}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="2424206" y="158472548"/>
+                <a:ext cx="1804985" cy="660807"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="145" name="正方形/長方形 144">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F74589-E594-4676-BCF5-91CC8FBD431F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2448890" y="158704170"/>
+              <a:ext cx="1705390" cy="206512"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="146" name="コネクタ: カギ線 145">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B6395C5-5D71-4675-BC97-1592D6659DE8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="153" idx="1"/>
+              <a:endCxn id="145" idx="2"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="10800000">
+              <a:off x="3300344" y="158910683"/>
+              <a:ext cx="1890645" cy="2300064"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector2">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="153" name="正方形/長方形 152">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD13DF62-9033-4F12-A60D-EFEE7C2EFB6D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5190988" y="161163552"/>
+              <a:ext cx="92334" cy="96597"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="137" name="図 136">
+          <xdr:cNvPr id="169" name="図 168">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F48E4675-205D-936B-1AC4-884485AC4E04}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37B08159-1208-46DE-A148-5E628B454B0A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9064,76 +9707,21 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="157099001"/>
-            <a:ext cx="10801350" cy="2971515"/>
+            <a:off x="484840" y="188279740"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="138" name="正方形/長方形 137">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16683198-05AC-4125-910E-AEF6CFBDB750}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5258546" y="157578612"/>
-            <a:ext cx="3356537" cy="663014"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -11719,6 +12307,7 @@
         <v>165</v>
       </c>
     </row>
+    <row r="695" spans="2:2" ht="4" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="708" spans="1:82" s="4" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="709" spans="1:82" s="6" customFormat="1" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="710" spans="1:82" x14ac:dyDescent="0.55000000000000004">
